--- a/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,51; 40,99</t>
+          <t>26,48; 40,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,92; 49,82</t>
+          <t>34,22; 50,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,05; 49,75</t>
+          <t>33,73; 50,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 37,6</t>
+          <t>24,12; 39,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,69; 54,1</t>
+          <t>40,31; 53,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,83; 57,54</t>
+          <t>40,78; 57,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,73; 58,49</t>
+          <t>42,49; 58,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 48,45</t>
+          <t>26,31; 47,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 45,25</t>
+          <t>35,73; 45,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,64; 52,2</t>
+          <t>40,39; 51,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,57; 52,38</t>
+          <t>40,79; 52,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 41,4</t>
+          <t>27,85; 41,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,95; 43,58</t>
+          <t>32,01; 43,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 46,98</t>
+          <t>34,34; 47,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,56; 34,85</t>
+          <t>23,02; 33,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 34,79</t>
+          <t>22,78; 34,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,61; 54,27</t>
+          <t>43,02; 55,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,29; 61,84</t>
+          <t>49,98; 62,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,78; 51,61</t>
+          <t>38,95; 50,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,35; 48,51</t>
+          <t>34,71; 48,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,94; 47,6</t>
+          <t>39,45; 47,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,4; 53,02</t>
+          <t>44,14; 53,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,14; 41,61</t>
+          <t>33,48; 41,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 40,62</t>
+          <t>30,93; 40,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 41,41</t>
+          <t>26,74; 40,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,39</t>
+          <t>34,02; 48,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,04; 40,83</t>
+          <t>26,92; 40,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 36,24</t>
+          <t>14,13; 36,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,06; 52,29</t>
+          <t>37,86; 52,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,37; 54,47</t>
+          <t>40,27; 54,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,07; 46,97</t>
+          <t>31,91; 45,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 47,73</t>
+          <t>31,48; 48,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,49; 44,41</t>
+          <t>34,14; 44,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 49,39</t>
+          <t>39,27; 49,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,02; 41,53</t>
+          <t>31,69; 40,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,03; 38,74</t>
+          <t>24,82; 39,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 42,21</t>
+          <t>29,03; 42,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,61; 50,92</t>
+          <t>37,88; 51,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,96; 44,11</t>
+          <t>31,43; 44,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 35,54</t>
+          <t>21,58; 35,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,2; 47,0</t>
+          <t>35,3; 47,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,77; 54,8</t>
+          <t>41,46; 54,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,01; 52,03</t>
+          <t>38,81; 51,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 43,99</t>
+          <t>29,4; 43,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,0; 42,56</t>
+          <t>33,73; 42,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41,22; 51,27</t>
+          <t>41,11; 50,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,24; 46,34</t>
+          <t>37,67; 46,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 38,32</t>
+          <t>27,69; 37,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,29; 38,59</t>
+          <t>32,38; 38,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,97; 45,71</t>
+          <t>38,24; 45,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,75; 38,2</t>
+          <t>31,34; 38,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,63; 32,22</t>
+          <t>24,07; 32,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,26; 48,48</t>
+          <t>42,27; 48,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,95; 54,25</t>
+          <t>46,84; 53,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,18; 48,25</t>
+          <t>41,28; 48,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,86; 42,9</t>
+          <t>35,21; 43,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,08; 42,61</t>
+          <t>38,2; 42,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,86; 49,11</t>
+          <t>43,85; 48,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,54; 42,22</t>
+          <t>37,7; 42,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 36,92</t>
+          <t>30,95; 36,93</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>39276</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42477</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41944</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29648</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62941</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53883</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53276</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>46375</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>102217</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>96360</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>95220</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>76023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>31272; 48074</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34371; 50573</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33582; 50138</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23466; 38061</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>53869; 71860</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>44412; 62837</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>45140; 61743</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>32180; 58331</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>89939; 115096</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>84547; 108836</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>83949; 107223</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>61155; 90113</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>64293</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47325</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87670</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93370</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81061</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>88864</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>151963</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>157319</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>127246</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>136189</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>54557; 74044</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53637; 73980</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37245; 54921</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38345; 58777</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>77702; 100364</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>83805; 104314</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>69977; 91510</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>75145; 104722</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>138489; 166553</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>142938; 172785</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>114325; 142974</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>119022; 154215</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47949</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41890</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45507</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54196</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58608</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51881</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>63719</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>92006</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>106557</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>93771</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>109226</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>30310; 45352</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39809; 56777</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33207; 49499</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23531; 60260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>45610; 63052</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>49988; 68054</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>42784; 61478</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>51572; 78690</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>79823; 103691</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>94689; 119685</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>81579; 104958</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>81993; 129399</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>62345</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67792</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59847</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40522</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70183</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75130</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74955</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>55643</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>132528</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142921</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134802</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96166</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>51142; 74516</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58110; 78241</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>50199; 70532</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30903; 50942</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>60253; 81246</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>64642; 85698</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>63639; 85011</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>44181; 65714</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>117010; 146857</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>127154; 157452</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>121932; 149903</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>81248; 110982</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>203724</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222166</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>189866</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>163002</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>254601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>478715</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>503157</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>451038</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>417604</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>187155; 221822</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>201556; 239622</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>170642; 208172</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138492; 185800</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>255946; 295496</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>260698; 298687</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>241033; 280406</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>229878; 282178</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>452143; 506013</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>475219; 527639</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>425364; 481685</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>380194; 453554</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,48; 40,71</t>
+          <t>26,29; 39,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,22; 50,35</t>
+          <t>34,43; 50,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,73; 50,36</t>
+          <t>33,19; 50,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 39,12</t>
+          <t>23,31; 37,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,31; 53,77</t>
+          <t>39,42; 53,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,78; 57,7</t>
+          <t>41,33; 57,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,49; 58,12</t>
+          <t>41,92; 58,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,31; 47,69</t>
+          <t>26,68; 48,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,73; 45,72</t>
+          <t>35,33; 45,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,39; 51,99</t>
+          <t>40,11; 51,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,79; 52,1</t>
+          <t>40,49; 52,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 41,04</t>
+          <t>27,74; 40,68</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,01; 43,44</t>
+          <t>32,18; 43,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 47,37</t>
+          <t>34,77; 47,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,02; 33,94</t>
+          <t>22,86; 34,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,78; 34,91</t>
+          <t>22,21; 33,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,02; 55,56</t>
+          <t>42,55; 54,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,98; 62,22</t>
+          <t>49,1; 61,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,95; 50,94</t>
+          <t>38,93; 51,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 48,37</t>
+          <t>35,31; 48,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,45; 47,44</t>
+          <t>39,24; 47,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,14; 53,35</t>
+          <t>44,41; 53,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,48; 41,87</t>
+          <t>33,05; 41,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 40,07</t>
+          <t>30,62; 40,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 40,0</t>
+          <t>26,99; 40,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,02; 48,53</t>
+          <t>33,85; 48,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 40,13</t>
+          <t>27,7; 41,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 36,18</t>
+          <t>15,88; 36,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,86; 52,34</t>
+          <t>37,46; 52,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,27; 54,83</t>
+          <t>39,81; 54,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,91; 45,85</t>
+          <t>31,6; 45,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,48; 48,04</t>
+          <t>31,8; 48,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,14; 44,34</t>
+          <t>34,62; 44,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,27; 49,63</t>
+          <t>39,38; 49,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,69; 40,77</t>
+          <t>31,93; 41,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,82; 39,17</t>
+          <t>24,57; 39,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,03; 42,3</t>
+          <t>29,48; 41,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,88; 51,0</t>
+          <t>36,99; 50,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,43; 44,16</t>
+          <t>31,37; 43,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,58; 35,58</t>
+          <t>21,98; 35,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 47,59</t>
+          <t>34,49; 46,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,46; 54,96</t>
+          <t>41,57; 54,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,81; 51,84</t>
+          <t>39,2; 51,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,4; 43,74</t>
+          <t>30,53; 44,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,73; 42,34</t>
+          <t>33,97; 42,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41,11; 50,9</t>
+          <t>41,57; 50,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,67; 46,31</t>
+          <t>37,19; 46,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,69; 37,82</t>
+          <t>28,44; 37,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,37</t>
+          <t>32,24; 38,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 45,47</t>
+          <t>38,77; 45,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,34; 38,24</t>
+          <t>31,33; 38,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,07; 32,29</t>
+          <t>23,7; 32,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,27; 48,81</t>
+          <t>41,92; 48,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,84; 53,66</t>
+          <t>47,09; 53,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,28; 48,02</t>
+          <t>41,36; 48,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,21; 43,22</t>
+          <t>35,05; 42,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,2; 42,75</t>
+          <t>38,05; 42,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,85; 48,69</t>
+          <t>43,8; 48,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,7; 42,69</t>
+          <t>37,46; 42,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,95; 36,93</t>
+          <t>30,92; 36,9</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31272; 48074</t>
+          <t>31050; 47156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34371; 50573</t>
+          <t>34578; 50524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33582; 50138</t>
+          <t>33038; 49919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23466; 38061</t>
+          <t>22676; 36784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53869; 71860</t>
+          <t>52679; 71557</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44412; 62837</t>
+          <t>45010; 62813</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45140; 61743</t>
+          <t>44538; 61995</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32180; 58331</t>
+          <t>32632; 59318</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89939; 115096</t>
+          <t>88933; 114762</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84547; 108836</t>
+          <t>83975; 107585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83949; 107223</t>
+          <t>83320; 107659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61155; 90113</t>
+          <t>60909; 89339</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54557; 74044</t>
+          <t>54855; 74010</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53637; 73980</t>
+          <t>54299; 73676</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37245; 54921</t>
+          <t>36991; 55009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38345; 58777</t>
+          <t>37399; 56941</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77702; 100364</t>
+          <t>76857; 98637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83805; 104314</t>
+          <t>82320; 103395</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69977; 91510</t>
+          <t>69942; 92608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75145; 104722</t>
+          <t>76441; 104485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138489; 166553</t>
+          <t>137771; 167662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142938; 172785</t>
+          <t>143820; 171729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114325; 142974</t>
+          <t>112841; 141777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119022; 154215</t>
+          <t>117834; 154192</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30310; 45352</t>
+          <t>30600; 46316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39809; 56777</t>
+          <t>39605; 56553</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33207; 49499</t>
+          <t>34164; 51038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23531; 60260</t>
+          <t>26439; 60001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45610; 63052</t>
+          <t>45132; 62894</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49988; 68054</t>
+          <t>49413; 67784</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42784; 61478</t>
+          <t>42364; 61141</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51572; 78690</t>
+          <t>52083; 78964</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79823; 103691</t>
+          <t>80957; 103567</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94689; 119685</t>
+          <t>94954; 118182</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81579; 104958</t>
+          <t>82198; 105572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81993; 129399</t>
+          <t>81158; 128821</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51142; 74516</t>
+          <t>51934; 73425</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58110; 78241</t>
+          <t>56752; 78029</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50199; 70532</t>
+          <t>50100; 69949</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30903; 50942</t>
+          <t>31466; 50617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60253; 81246</t>
+          <t>58884; 79396</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64642; 85698</t>
+          <t>64807; 85495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63639; 85011</t>
+          <t>64285; 84922</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44181; 65714</t>
+          <t>45876; 67113</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117010; 146857</t>
+          <t>117828; 148500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127154; 157452</t>
+          <t>128583; 157089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121932; 149903</t>
+          <t>120390; 149493</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81248; 110982</t>
+          <t>83446; 110607</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>187155; 221822</t>
+          <t>186354; 221172</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>201556; 239622</t>
+          <t>204318; 242337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170642; 208172</t>
+          <t>170586; 208083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138492; 185800</t>
+          <t>136345; 185752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>255946; 295496</t>
+          <t>253811; 293625</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>260698; 298687</t>
+          <t>262113; 300282</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>241033; 280406</t>
+          <t>241538; 281183</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>229878; 282178</t>
+          <t>228801; 279715</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>452143; 506013</t>
+          <t>450305; 505438</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>475219; 527639</t>
+          <t>474635; 526569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>425364; 481685</t>
+          <t>422726; 477154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>380194; 453554</t>
+          <t>379725; 453220</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47,1%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33,26%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42,29%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>42,13%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,15%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 39,93</t>
+          <t>39,69; 54,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,43; 50,31</t>
+          <t>40,83; 57,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,19; 50,14</t>
+          <t>41,73; 58,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 37,81</t>
+          <t>30,09; 49,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,42; 53,54</t>
+          <t>26,51; 40,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,33; 57,68</t>
+          <t>33,92; 49,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,92; 58,36</t>
+          <t>33,05; 49,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 48,5</t>
+          <t>22,57; 36,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 45,59</t>
+          <t>35,68; 45,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,11; 51,39</t>
+          <t>40,64; 52,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,49; 52,31</t>
+          <t>40,57; 52,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,74; 40,68</t>
+          <t>29,16; 41,64</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41,27%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>37,72%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>40,95%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>28,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,18; 43,42</t>
+          <t>42,61; 54,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 47,17</t>
+          <t>49,29; 61,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,86; 34,0</t>
+          <t>38,78; 51,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,21; 33,82</t>
+          <t>35,29; 48,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,55; 54,61</t>
+          <t>31,95; 43,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,1; 61,67</t>
+          <t>34,62; 46,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,93; 51,55</t>
+          <t>23,56; 34,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 48,26</t>
+          <t>22,98; 34,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,24; 47,76</t>
+          <t>38,94; 47,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,41; 53,03</t>
+          <t>44,4; 53,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 41,52</t>
+          <t>33,14; 41,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 40,06</t>
+          <t>30,91; 40,65</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44,99%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>33,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,99; 40,85</t>
+          <t>38,06; 52,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 48,33</t>
+          <t>40,37; 54,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,7; 41,38</t>
+          <t>32,07; 46,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 36,03</t>
+          <t>31,12; 48,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,46; 52,21</t>
+          <t>27,36; 41,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,81; 54,61</t>
+          <t>34,46; 48,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 45,6</t>
+          <t>28,04; 40,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,8; 48,21</t>
+          <t>23,55; 36,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,62; 44,29</t>
+          <t>34,49; 44,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,38; 49,01</t>
+          <t>39,13; 49,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 41,01</t>
+          <t>32,02; 41,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,57; 39,0</t>
+          <t>29,88; 40,57</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 41,68</t>
+          <t>35,2; 47,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,99; 50,86</t>
+          <t>41,77; 54,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,37; 43,8</t>
+          <t>39,01; 52,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,98; 35,35</t>
+          <t>29,92; 43,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,49; 46,51</t>
+          <t>29,48; 42,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,57; 54,83</t>
+          <t>37,61; 50,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 51,79</t>
+          <t>30,96; 44,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 44,67</t>
+          <t>20,27; 32,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,97; 42,81</t>
+          <t>34,0; 42,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41,57; 50,78</t>
+          <t>41,22; 51,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,19; 46,19</t>
+          <t>37,24; 46,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,44; 37,69</t>
+          <t>27,0; 36,63</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,26</t>
+          <t>42,26; 48,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,98</t>
+          <t>46,95; 54,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,22</t>
+          <t>41,18; 48,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,7; 32,28</t>
+          <t>35,32; 43,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,5</t>
+          <t>32,29; 38,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 53,95</t>
+          <t>38,97; 45,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,36; 48,15</t>
+          <t>31,75; 38,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,05; 42,85</t>
+          <t>25,56; 31,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,05; 42,71</t>
+          <t>38,08; 42,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,8; 48,59</t>
+          <t>43,86; 49,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 42,29</t>
+          <t>37,54; 42,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,9</t>
+          <t>31,8; 36,74</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62941</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53276</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44524</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>39276</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>42477</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>41944</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29648</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>62941</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53883</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53276</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>74651</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31050; 47156</t>
+          <t>53047; 72298</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34578; 50524</t>
+          <t>44462; 62657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33038; 49919</t>
+          <t>44332; 62134</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22676; 36784</t>
+          <t>33377; 55139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52679; 71557</t>
+          <t>31302; 48403</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45010; 62813</t>
+          <t>34072; 50034</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44538; 61995</t>
+          <t>32905; 49526</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32632; 59318</t>
+          <t>22894; 37346</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88933; 114762</t>
+          <t>89814; 113911</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83975; 107585</t>
+          <t>85077; 109277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83320; 107659</t>
+          <t>83486; 107783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60909; 89339</t>
+          <t>61928; 88424</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87670</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93370</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81061</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84249</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>64293</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>63949</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>46185</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47325</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87670</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93370</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81061</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>136189</t>
+          <t>130843</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54855; 74010</t>
+          <t>76973; 98036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54299; 73676</t>
+          <t>82634; 103692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36991; 55009</t>
+          <t>69676; 92718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37399; 56941</t>
+          <t>72042; 99189</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76857; 98637</t>
+          <t>54455; 74276</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82320; 103395</t>
+          <t>54075; 73378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69942; 92608</t>
+          <t>38121; 56393</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76441; 104485</t>
+          <t>37798; 57506</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137771; 167662</t>
+          <t>136726; 167120</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143820; 171729</t>
+          <t>143795; 171690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112841; 141777</t>
+          <t>113142; 142071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>117834; 154192</t>
+          <t>113944; 149856</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58608</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51881</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>59102</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>37810</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>47949</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>41890</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45507</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54196</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58608</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>51881</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63719</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>100082</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30600; 46316</t>
+          <t>45847; 62988</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39605; 56553</t>
+          <t>50106; 67609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34164; 51038</t>
+          <t>42990; 62971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26439; 60001</t>
+          <t>46990; 72558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45132; 62894</t>
+          <t>31018; 46950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49413; 67784</t>
+          <t>40316; 56620</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42364; 61141</t>
+          <t>34582; 50366</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52083; 78964</t>
+          <t>31958; 50074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80957; 103567</t>
+          <t>80654; 103848</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94954; 118182</t>
+          <t>94351; 119091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82198; 105572</t>
+          <t>82417; 106918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81158; 128821</t>
+          <t>85670; 116302</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>70183</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75130</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74955</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51243</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>62345</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>67792</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>59847</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40522</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70183</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75130</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74955</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55643</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96166</t>
+          <t>89047</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51934; 73425</t>
+          <t>60098; 80231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56752; 78029</t>
+          <t>65131; 85438</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50100; 69949</t>
+          <t>63961; 85308</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31466; 50617</t>
+          <t>42263; 61141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58884; 79396</t>
+          <t>51923; 74356</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64807; 85495</t>
+          <t>57698; 78112</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64285; 84922</t>
+          <t>49450; 70439</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45876; 67113</t>
+          <t>29031; 46807</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117828; 148500</t>
+          <t>117933; 147622</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128583; 157089</t>
+          <t>127498; 158609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120390; 149493</t>
+          <t>120530; 149983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83446; 110607</t>
+          <t>76810; 104203</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>163002</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155504</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>394622</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186354; 221172</t>
+          <t>255865; 293526</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204318; 242337</t>
+          <t>261343; 301978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170586; 208083</t>
+          <t>240456; 281764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136345; 185752</t>
+          <t>214496; 262239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>253811; 293625</t>
+          <t>186635; 223096</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>262113; 300282</t>
+          <t>205399; 240883</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>241538; 281183</t>
+          <t>172831; 207961</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>228801; 279715</t>
+          <t>139280; 173325</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>450305; 505438</t>
+          <t>450692; 504253</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>474635; 526569</t>
+          <t>475291; 532153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>422726; 477154</t>
+          <t>423582; 476396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>379725; 453220</t>
+          <t>366438; 423257</t>
         </is>
       </c>
     </row>
